--- a/testing_sustainability_data_report_updated.xlsx
+++ b/testing_sustainability_data_report_updated.xlsx
@@ -378,7 +378,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="89">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -627,6 +627,9 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="3" fontId="4" fillId="19" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="4" fillId="19" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -13349,7 +13352,9 @@
       <c r="L112" s="77" t="n">
         <v>77615</v>
       </c>
-      <c r="M112" s="77" t="n"/>
+      <c r="M112" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N112" s="77" t="n">
         <v>87303</v>
       </c>
@@ -13463,7 +13468,9 @@
       <c r="L113" s="77" t="n">
         <v>84792</v>
       </c>
-      <c r="M113" s="77" t="n"/>
+      <c r="M113" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N113" s="77" t="n">
         <v>105975</v>
       </c>
@@ -13577,7 +13584,9 @@
       <c r="L114" s="77" t="n">
         <v>129786</v>
       </c>
-      <c r="M114" s="77" t="n"/>
+      <c r="M114" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N114" s="77" t="n">
         <v>162347</v>
       </c>
@@ -13691,7 +13700,9 @@
       <c r="L115" s="77" t="n">
         <v>153093</v>
       </c>
-      <c r="M115" s="77" t="n"/>
+      <c r="M115" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N115" s="77" t="n">
         <v>185045</v>
       </c>
@@ -13808,7 +13819,9 @@
       <c r="L116" s="77" t="n">
         <v>149108</v>
       </c>
-      <c r="M116" s="77" t="n"/>
+      <c r="M116" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N116" s="77" t="n">
         <v>186865</v>
       </c>
@@ -13922,7 +13935,9 @@
       <c r="L117" s="77" t="n">
         <v>196791</v>
       </c>
-      <c r="M117" s="77" t="n"/>
+      <c r="M117" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N117" s="77" t="n">
         <v>245701</v>
       </c>
@@ -14036,7 +14051,9 @@
       <c r="L118" s="77" t="n">
         <v>133636</v>
       </c>
-      <c r="M118" s="77" t="n"/>
+      <c r="M118" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N118" s="77" t="n">
         <v>172602</v>
       </c>
@@ -14150,7 +14167,9 @@
       <c r="L119" s="77" t="n">
         <v>129915</v>
       </c>
-      <c r="M119" s="77" t="n"/>
+      <c r="M119" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N119" s="77" t="n">
         <v>161279</v>
       </c>
@@ -14264,7 +14283,9 @@
       <c r="L120" s="77" t="n">
         <v>114445</v>
       </c>
-      <c r="M120" s="77" t="n"/>
+      <c r="M120" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N120" s="77" t="n">
         <v>110214</v>
       </c>
@@ -14378,7 +14399,9 @@
       <c r="L121" s="77" t="n">
         <v>92079</v>
       </c>
-      <c r="M121" s="77" t="n"/>
+      <c r="M121" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N121" s="77" t="n">
         <v>63014</v>
       </c>
@@ -14492,7 +14515,9 @@
       <c r="L122" s="60" t="n">
         <v>88012</v>
       </c>
-      <c r="M122" s="60" t="n"/>
+      <c r="M122" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N122" s="60" t="n">
         <v>40751</v>
       </c>
@@ -14606,7 +14631,9 @@
       <c r="L123" s="60" t="n">
         <v>71168</v>
       </c>
-      <c r="M123" s="60" t="n"/>
+      <c r="M123" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N123" s="60" t="n">
         <v>59396</v>
       </c>
@@ -14722,7 +14749,9 @@
       <c r="L124" s="60" t="n">
         <v>88712</v>
       </c>
-      <c r="M124" s="60" t="n"/>
+      <c r="M124" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N124" s="60" t="n">
         <v>72772</v>
       </c>
@@ -14838,7 +14867,9 @@
       <c r="L125" s="60" t="n">
         <v>116672</v>
       </c>
-      <c r="M125" s="60" t="n"/>
+      <c r="M125" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N125" s="60" t="n">
         <v>116582</v>
       </c>
@@ -14954,7 +14985,9 @@
       <c r="L126" s="60" t="n">
         <v>113551</v>
       </c>
-      <c r="M126" s="60" t="n"/>
+      <c r="M126" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N126" s="60" t="n">
         <v>101590</v>
       </c>
@@ -15072,7 +15105,9 @@
       <c r="L127" s="60" t="n">
         <v>167321</v>
       </c>
-      <c r="M127" s="60" t="n"/>
+      <c r="M127" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N127" s="60" t="n">
         <v>166930</v>
       </c>
@@ -15195,7 +15230,9 @@
       <c r="L128" s="60" t="n">
         <v>148622</v>
       </c>
-      <c r="M128" s="60" t="n"/>
+      <c r="M128" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N128" s="60" t="n">
         <v>146460</v>
       </c>
@@ -15315,7 +15352,9 @@
       <c r="L129" s="60" t="n">
         <v>181289</v>
       </c>
-      <c r="M129" s="60" t="n"/>
+      <c r="M129" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N129" s="60" t="n">
         <v>171979</v>
       </c>
@@ -15436,7 +15475,9 @@
       <c r="L130" s="60" t="n">
         <v>163882</v>
       </c>
-      <c r="M130" s="60" t="n"/>
+      <c r="M130" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N130" s="60" t="n">
         <v>166126</v>
       </c>
@@ -15556,7 +15597,9 @@
       <c r="L131" s="60" t="n">
         <v>117930</v>
       </c>
-      <c r="M131" s="60" t="n"/>
+      <c r="M131" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N131" s="60" t="n">
         <v>120288</v>
       </c>
@@ -15676,7 +15719,9 @@
       <c r="L132" s="60" t="n">
         <v>116907</v>
       </c>
-      <c r="M132" s="60" t="n"/>
+      <c r="M132" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N132" s="60" t="n">
         <v>108966</v>
       </c>
@@ -15796,7 +15841,9 @@
       <c r="L133" s="60" t="n">
         <v>75231</v>
       </c>
-      <c r="M133" s="60" t="n"/>
+      <c r="M133" s="60" t="n">
+        <v>0</v>
+      </c>
       <c r="N133" s="60" t="n">
         <v>47641</v>
       </c>
@@ -15916,7 +15963,9 @@
       <c r="L134" s="51" t="n">
         <v>83004</v>
       </c>
-      <c r="M134" s="51" t="n"/>
+      <c r="M134" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N134" s="51" t="n">
         <v>51613</v>
       </c>
@@ -16035,7 +16084,9 @@
       <c r="L135" s="51" t="n">
         <v>79071</v>
       </c>
-      <c r="M135" s="51" t="n"/>
+      <c r="M135" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N135" s="51" t="n">
         <v>48514</v>
       </c>
@@ -16155,7 +16206,9 @@
       <c r="L136" s="51" t="n">
         <v>76787</v>
       </c>
-      <c r="M136" s="51" t="n"/>
+      <c r="M136" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N136" s="51" t="n">
         <v>66365</v>
       </c>
@@ -16245,7 +16298,7 @@
         <v>8751020</v>
       </c>
       <c r="C137" s="51" t="n">
-        <v>3603467</v>
+        <v>3603466.9</v>
       </c>
       <c r="D137" s="51" t="n">
         <v>558983</v>
@@ -16272,9 +16325,11 @@
         <v>46949</v>
       </c>
       <c r="L137" s="51" t="n">
-        <v>86079</v>
-      </c>
-      <c r="M137" s="51" t="n"/>
+        <v>86079.10000000001</v>
+      </c>
+      <c r="M137" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N137" s="51" t="n">
         <v>81173</v>
       </c>
@@ -16335,10 +16390,10 @@
         <v>0</v>
       </c>
       <c r="AI137" s="51" t="n">
-        <v>11196</v>
+        <v>11196.33</v>
       </c>
       <c r="AJ137" s="51" t="n">
-        <v>28426</v>
+        <v>28426.29</v>
       </c>
       <c r="AK137" t="n">
         <v>0</v>
@@ -16393,7 +16448,9 @@
       <c r="L138" s="51" t="n">
         <v>128987</v>
       </c>
-      <c r="M138" s="51" t="n"/>
+      <c r="M138" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N138" s="51" t="n">
         <v>145549</v>
       </c>
@@ -16454,9 +16511,9 @@
         <v>0</v>
       </c>
       <c r="AI138" s="51" t="n">
-        <v>14242</v>
-      </c>
-      <c r="AJ138" s="51" t="n">
+        <v>14241.92</v>
+      </c>
+      <c r="AJ138" s="83" t="n">
         <v>5518</v>
       </c>
       <c r="AK138" t="n">
@@ -16512,7 +16569,9 @@
       <c r="L139" s="51" t="n">
         <v>128696</v>
       </c>
-      <c r="M139" s="51" t="n"/>
+      <c r="M139" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N139" s="51" t="n">
         <v>189802</v>
       </c>
@@ -16573,9 +16632,9 @@
         <v>0</v>
       </c>
       <c r="AI139" s="51" t="n">
-        <v>14634</v>
-      </c>
-      <c r="AJ139" s="56" t="n">
+        <v>14634.33</v>
+      </c>
+      <c r="AJ139" s="84" t="n">
         <v>41355</v>
       </c>
       <c r="AK139" t="n">
@@ -16635,7 +16694,9 @@
       <c r="L140" s="51" t="n">
         <v>145108</v>
       </c>
-      <c r="M140" s="51" t="n"/>
+      <c r="M140" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N140" s="51" t="n">
         <v>265504</v>
       </c>
@@ -16755,7 +16816,9 @@
       <c r="L141" s="51" t="n">
         <v>173834</v>
       </c>
-      <c r="M141" s="51" t="n"/>
+      <c r="M141" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N141" s="51" t="n">
         <v>300733</v>
       </c>
@@ -16876,7 +16939,9 @@
       <c r="L142" s="51" t="n">
         <v>142935</v>
       </c>
-      <c r="M142" s="51" t="n"/>
+      <c r="M142" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N142" s="51" t="n">
         <v>268527</v>
       </c>
@@ -16997,7 +17062,9 @@
       <c r="L143" s="51" t="n">
         <v>143945</v>
       </c>
-      <c r="M143" s="51" t="n"/>
+      <c r="M143" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N143" s="51" t="n">
         <v>251737</v>
       </c>
@@ -17118,7 +17185,9 @@
       <c r="L144" s="51" t="n">
         <v>85990</v>
       </c>
-      <c r="M144" s="51" t="n"/>
+      <c r="M144" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N144" s="51" t="n">
         <v>105031</v>
       </c>
@@ -17239,7 +17308,9 @@
       <c r="L145" s="51" t="n">
         <v>81529</v>
       </c>
-      <c r="M145" s="51" t="n"/>
+      <c r="M145" s="51" t="n">
+        <v>0</v>
+      </c>
       <c r="N145" s="51" t="n">
         <v>63573</v>
       </c>
@@ -17360,7 +17431,9 @@
       <c r="L146" s="77" t="n">
         <v>102592</v>
       </c>
-      <c r="M146" s="77" t="n"/>
+      <c r="M146" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N146" s="83" t="n">
         <v>56618</v>
       </c>
@@ -17481,7 +17554,9 @@
       <c r="L147" s="77" t="n">
         <v>81167</v>
       </c>
-      <c r="M147" s="77" t="n"/>
+      <c r="M147" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N147" s="77" t="n">
         <v>57790</v>
       </c>
@@ -17600,7 +17675,9 @@
       <c r="L148" s="77" t="n">
         <v>79410</v>
       </c>
-      <c r="M148" s="77" t="n"/>
+      <c r="M148" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N148" s="77" t="n">
         <v>103510</v>
       </c>
@@ -17719,7 +17796,9 @@
       <c r="L149" s="77" t="n">
         <v>118081</v>
       </c>
-      <c r="M149" s="77" t="n"/>
+      <c r="M149" s="77" t="n">
+        <v>0</v>
+      </c>
       <c r="N149" s="77" t="n">
         <v>208610</v>
       </c>
@@ -17840,9 +17919,6 @@
       <c r="AH150" s="77" t="n"/>
       <c r="AI150" s="77" t="n"/>
       <c r="AJ150" s="77" t="n"/>
-      <c r="AK150" t="n">
-        <v>0</v>
-      </c>
       <c r="AL150" s="25">
         <f>SUM(B139:B150)</f>
         <v/>
@@ -17895,9 +17971,6 @@
       <c r="AH151" s="77" t="n"/>
       <c r="AI151" s="77" t="n"/>
       <c r="AJ151" s="79" t="n"/>
-      <c r="AK151" t="n">
-        <v>0</v>
-      </c>
       <c r="AL151" s="41">
         <f>SUM(B140:B151)</f>
         <v/>
@@ -17927,7 +18000,7 @@
     </row>
     <row r="156"/>
     <row r="157">
-      <c r="A157" s="84" t="n">
+      <c r="A157" s="85" t="n">
         <v>2023</v>
       </c>
       <c r="B157" s="25">
@@ -18023,7 +18096,7 @@
         <f>SUM(AB110:AB121)</f>
         <v/>
       </c>
-      <c r="AC157" s="85" t="n"/>
+      <c r="AC157" s="86" t="n"/>
       <c r="AD157" s="25">
         <f>SUM(AD110:AD121)</f>
         <v/>
@@ -18039,7 +18112,7 @@
       <c r="AJ157" s="25" t="n"/>
     </row>
     <row r="158">
-      <c r="A158" s="84" t="n">
+      <c r="A158" s="85" t="n">
         <v>2024</v>
       </c>
       <c r="B158" s="25">
@@ -18135,7 +18208,7 @@
         <f>SUM(AB122:AB133)</f>
         <v/>
       </c>
-      <c r="AC158" s="85" t="n"/>
+      <c r="AC158" s="86" t="n"/>
       <c r="AD158" s="25">
         <f>SUM(AD122:AD133)</f>
         <v/>
@@ -18151,113 +18224,113 @@
       <c r="AJ158" s="25" t="n"/>
     </row>
     <row r="159">
-      <c r="B159" s="86">
+      <c r="B159" s="87">
         <f>(B158-B157)/B157</f>
         <v/>
       </c>
-      <c r="C159" s="86">
+      <c r="C159" s="87">
         <f>(C158-C157)/C157</f>
         <v/>
       </c>
-      <c r="D159" s="86">
+      <c r="D159" s="87">
         <f>(D158-D157)/D157</f>
         <v/>
       </c>
-      <c r="E159" s="86">
+      <c r="E159" s="87">
         <f>(E158-E157)/E157</f>
         <v/>
       </c>
-      <c r="F159" s="86">
+      <c r="F159" s="87">
         <f>(F158-F157)/F157</f>
         <v/>
       </c>
-      <c r="G159" s="86">
+      <c r="G159" s="87">
         <f>(G158-G157)/G157</f>
         <v/>
       </c>
-      <c r="H159" s="86">
+      <c r="H159" s="87">
         <f>(H158-H157)/H157</f>
         <v/>
       </c>
-      <c r="I159" s="86">
+      <c r="I159" s="87">
         <f>(I158-I157)/I157</f>
         <v/>
       </c>
-      <c r="J159" s="86">
+      <c r="J159" s="87">
         <f>(J158-J157)/J157</f>
         <v/>
       </c>
-      <c r="K159" s="86">
+      <c r="K159" s="87">
         <f>(K158-K157)/K157</f>
         <v/>
       </c>
-      <c r="L159" s="86">
+      <c r="L159" s="87">
         <f>(L158-L157)/L157</f>
         <v/>
       </c>
-      <c r="M159" s="86">
+      <c r="M159" s="87">
         <f>(M158-M157)/M157</f>
         <v/>
       </c>
-      <c r="N159" s="86">
+      <c r="N159" s="87">
         <f>(N158-N157)/N157</f>
         <v/>
       </c>
-      <c r="O159" s="86">
+      <c r="O159" s="87">
         <f>(O158-O157)/O157</f>
         <v/>
       </c>
-      <c r="P159" s="86">
+      <c r="P159" s="87">
         <f>(P158-P157)/P157</f>
         <v/>
       </c>
-      <c r="Q159" s="86">
+      <c r="Q159" s="87">
         <f>(Q158-Q157)/Q157</f>
         <v/>
       </c>
-      <c r="R159" s="86" t="n"/>
-      <c r="S159" s="86" t="n"/>
-      <c r="T159" s="86" t="n"/>
-      <c r="U159" s="86" t="n"/>
-      <c r="V159" s="86" t="n"/>
-      <c r="W159" s="86">
+      <c r="R159" s="87" t="n"/>
+      <c r="S159" s="87" t="n"/>
+      <c r="T159" s="87" t="n"/>
+      <c r="U159" s="87" t="n"/>
+      <c r="V159" s="87" t="n"/>
+      <c r="W159" s="87">
         <f>(W158-W157)/W157</f>
         <v/>
       </c>
-      <c r="X159" s="86">
+      <c r="X159" s="87">
         <f>(X158-X157)/X157</f>
         <v/>
       </c>
-      <c r="Y159" s="86">
+      <c r="Y159" s="87">
         <f>(Y158-Y157)/Y157</f>
         <v/>
       </c>
-      <c r="Z159" s="86">
+      <c r="Z159" s="87">
         <f>(Z158-Z157)/Z157</f>
         <v/>
       </c>
-      <c r="AA159" s="86">
+      <c r="AA159" s="87">
         <f>(AA158-AA157)/AA157</f>
         <v/>
       </c>
-      <c r="AB159" s="86">
+      <c r="AB159" s="87">
         <f>(AB158-AB157)/AB157</f>
         <v/>
       </c>
-      <c r="AC159" s="87" t="n"/>
-      <c r="AD159" s="86">
+      <c r="AC159" s="88" t="n"/>
+      <c r="AD159" s="87">
         <f>(AD158-AD157)/AD157</f>
         <v/>
       </c>
-      <c r="AE159" s="86">
+      <c r="AE159" s="87">
         <f>(AE158-AE157)/AE157</f>
         <v/>
       </c>
-      <c r="AF159" s="86" t="n"/>
-      <c r="AG159" s="86" t="n"/>
-      <c r="AH159" s="86" t="n"/>
-      <c r="AI159" s="86" t="n"/>
-      <c r="AJ159" s="86" t="n"/>
+      <c r="AF159" s="87" t="n"/>
+      <c r="AG159" s="87" t="n"/>
+      <c r="AH159" s="87" t="n"/>
+      <c r="AI159" s="87" t="n"/>
+      <c r="AJ159" s="87" t="n"/>
     </row>
     <row r="160">
       <c r="B160" s="25">
@@ -18353,7 +18426,7 @@
         <f>AB158-AB157</f>
         <v/>
       </c>
-      <c r="AC160" s="85" t="n"/>
+      <c r="AC160" s="86" t="n"/>
       <c r="AD160" s="25">
         <f>AD158-AD157</f>
         <v/>
@@ -18369,124 +18442,124 @@
       <c r="AJ160" s="25" t="n"/>
     </row>
     <row r="161">
-      <c r="C161" s="86">
+      <c r="C161" s="87">
         <f>C160/$B$160</f>
         <v/>
       </c>
-      <c r="D161" s="86">
+      <c r="D161" s="87">
         <f>D160/$B$160</f>
         <v/>
       </c>
-      <c r="E161" s="86">
+      <c r="E161" s="87">
         <f>E160/$B$160</f>
         <v/>
       </c>
-      <c r="F161" s="86">
+      <c r="F161" s="87">
         <f>F160/$B$160</f>
         <v/>
       </c>
-      <c r="G161" s="86">
+      <c r="G161" s="87">
         <f>G160/$B$160</f>
         <v/>
       </c>
-      <c r="H161" s="86">
+      <c r="H161" s="87">
         <f>H160/$B$160</f>
         <v/>
       </c>
-      <c r="I161" s="86">
+      <c r="I161" s="87">
         <f>I160/$B$160</f>
         <v/>
       </c>
-      <c r="J161" s="86">
+      <c r="J161" s="87">
         <f>J160/$B$160</f>
         <v/>
       </c>
-      <c r="K161" s="86">
+      <c r="K161" s="87">
         <f>K160/$B$160</f>
         <v/>
       </c>
-      <c r="L161" s="86">
+      <c r="L161" s="87">
         <f>L160/$B$160</f>
         <v/>
       </c>
-      <c r="M161" s="86">
+      <c r="M161" s="87">
         <f>M160/$B$160</f>
         <v/>
       </c>
-      <c r="N161" s="86">
+      <c r="N161" s="87">
         <f>N160/$B$160</f>
         <v/>
       </c>
-      <c r="O161" s="86">
+      <c r="O161" s="87">
         <f>O160/$B$160</f>
         <v/>
       </c>
-      <c r="P161" s="86">
+      <c r="P161" s="87">
         <f>P160/$B$160</f>
         <v/>
       </c>
-      <c r="Q161" s="86">
+      <c r="Q161" s="87">
         <f>Q160/$B$160</f>
         <v/>
       </c>
-      <c r="R161" s="86" t="n"/>
-      <c r="S161" s="86" t="n"/>
-      <c r="T161" s="86" t="n"/>
-      <c r="U161" s="86" t="n"/>
-      <c r="V161" s="86" t="n"/>
-      <c r="W161" s="86">
+      <c r="R161" s="87" t="n"/>
+      <c r="S161" s="87" t="n"/>
+      <c r="T161" s="87" t="n"/>
+      <c r="U161" s="87" t="n"/>
+      <c r="V161" s="87" t="n"/>
+      <c r="W161" s="87">
         <f>W160/$B$160</f>
         <v/>
       </c>
-      <c r="X161" s="86">
+      <c r="X161" s="87">
         <f>X160/$B$160</f>
         <v/>
       </c>
-      <c r="Y161" s="86">
+      <c r="Y161" s="87">
         <f>Y160/$B$160</f>
         <v/>
       </c>
-      <c r="Z161" s="86">
+      <c r="Z161" s="87">
         <f>Z160/$B$160</f>
         <v/>
       </c>
-      <c r="AA161" s="86">
+      <c r="AA161" s="87">
         <f>AA160/$B$160</f>
         <v/>
       </c>
-      <c r="AB161" s="86">
+      <c r="AB161" s="87">
         <f>AB160/$B$160</f>
         <v/>
       </c>
-      <c r="AC161" s="87" t="n"/>
-      <c r="AD161" s="86">
+      <c r="AC161" s="88" t="n"/>
+      <c r="AD161" s="87">
         <f>AD160/$B$160</f>
         <v/>
       </c>
-      <c r="AE161" s="86">
+      <c r="AE161" s="87">
         <f>AE160/$B$160</f>
         <v/>
       </c>
-      <c r="AF161" s="86" t="n"/>
-      <c r="AG161" s="86" t="n"/>
-      <c r="AH161" s="86" t="n"/>
-      <c r="AI161" s="86" t="n"/>
-      <c r="AJ161" s="86" t="n"/>
+      <c r="AF161" s="87" t="n"/>
+      <c r="AG161" s="87" t="n"/>
+      <c r="AH161" s="87" t="n"/>
+      <c r="AI161" s="87" t="n"/>
+      <c r="AJ161" s="87" t="n"/>
     </row>
     <row r="162"/>
     <row r="163"/>
     <row r="164">
-      <c r="B164" s="84" t="n">
+      <c r="B164" s="85" t="n">
         <v>8250000</v>
       </c>
     </row>
     <row r="165">
-      <c r="B165" s="84" t="n">
+      <c r="B165" s="85" t="n">
         <v>350000</v>
       </c>
     </row>
     <row r="166">
-      <c r="B166" s="84">
+      <c r="B166" s="85">
         <f>B165/B164</f>
         <v/>
       </c>
